--- a/templates/template.xlsx
+++ b/templates/template.xlsx
@@ -544,20 +544,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.14"/>
-    <col customWidth="1" min="2" max="2" width="10.0"/>
-    <col customWidth="1" min="3" max="3" width="15.14"/>
-    <col customWidth="1" min="4" max="4" width="26.71"/>
-    <col customWidth="1" min="5" max="5" width="22.57"/>
-    <col customWidth="1" min="6" max="6" width="59.43"/>
-    <col customWidth="1" min="7" max="7" width="16.71"/>
-    <col customWidth="1" min="8" max="8" width="43.57"/>
+    <col customWidth="1" min="1" max="1" width="6.92"/>
+    <col customWidth="1" min="2" max="2" width="9.22"/>
+    <col customWidth="1" min="3" max="3" width="11.17"/>
+    <col customWidth="1" min="4" max="4" width="34.82"/>
+    <col customWidth="1" min="5" max="5" width="34.82"/>
+    <col customWidth="1" min="6" max="6" width="52.2"/>
+    <col customWidth="1" min="7" max="7" width="14.61"/>
+    <col customWidth="1" min="8" max="8" width="37.52"/>
     <col customWidth="1" hidden="1" min="9" max="9" width="30.57"/>
     <col customWidth="1" min="10" max="29" width="11.57"/>
   </cols>
@@ -595,7 +595,7 @@
       <c r="AB1" s="5"/>
       <c r="AC1" s="5"/>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
